--- a/data/trans_dic/P13A_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P13A_1_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses)</t>
+          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,61</t>
+          <t>1,63; 9,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,6</t>
+          <t>0,69; 3,7</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,23</t>
+          <t>0,25; 3,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,04</t>
+          <t>0,61; 3,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,52</t>
+          <t>0,67; 2,27</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,93</t>
+          <t>0,52; 2,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,79</t>
+          <t>2,18; 4,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,24</t>
+          <t>1,58; 3,19</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,79</t>
+          <t>0,22; 1,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 8,49</t>
+          <t>4,37; 8,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,24</t>
+          <t>1,71; 4,25</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,2</t>
+          <t>0,97; 3,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 6,95</t>
+          <t>4,02; 6,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,62</t>
+          <t>2,8; 4,67</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,5</t>
+          <t>0,44; 2,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,59</t>
+          <t>1,06; 4,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,99</t>
+          <t>1,03; 3,14</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,4</t>
+          <t>0,77; 3,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,91</t>
+          <t>3,03; 5,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,32</t>
+          <t>2,32; 4,27</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,5</t>
+          <t>0,73; 1,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,75</t>
+          <t>3,18; 4,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 2,98</t>
+          <t>2,16; 2,98</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses)</t>
+          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4435</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5052; 26806</t>
+          <t>5077; 29381</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4711; 25605</t>
+          <t>4930; 26330</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1242; 13675</t>
+          <t>1074; 13483</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3293; 15565</t>
+          <t>3115; 15809</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6332; 23536</t>
+          <t>6261; 21200</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2694; 15633</t>
+          <t>2757; 15391</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11966; 25833</t>
+          <t>11744; 24564</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16409; 34796</t>
+          <t>16953; 34250</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1871; 15852</t>
+          <t>1962; 15200</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30715; 60368</t>
+          <t>31046; 60373</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27872; 67684</t>
+          <t>27368; 67966</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5154; 17867</t>
+          <t>5386; 17887</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22426; 37834</t>
+          <t>21886; 37952</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30826; 50933</t>
+          <t>30863; 51496</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1524; 9120</t>
+          <t>1589; 8778</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6479; 27886</t>
+          <t>6464; 28114</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8878; 29032</t>
+          <t>10048; 30578</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2295; 9551</t>
+          <t>2158; 9238</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12740; 25044</t>
+          <t>12835; 24742</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16240; 30451</t>
+          <t>16382; 30074</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>25102; 51787</t>
+          <t>25203; 51393</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>118711; 173404</t>
+          <t>116137; 172756</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>152673; 211370</t>
+          <t>153163; 211769</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P13A_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P13A_1_R-Edad-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 9,43</t>
+          <t>1,85; 8,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,7</t>
+          <t>0,89; 4,48</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,18</t>
+          <t>0,29; 3,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,09</t>
+          <t>0,85; 3,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,27</t>
+          <t>0,76; 2,45</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,88</t>
+          <t>0,45; 2,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,55</t>
+          <t>2,02; 4,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,19</t>
+          <t>1,42; 2,88</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,71</t>
+          <t>0,45; 2,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,49</t>
+          <t>4,39; 7,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,25</t>
+          <t>2,62; 4,31</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,21</t>
+          <t>0,95; 3,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 6,97</t>
+          <t>3,98; 7,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,67</t>
+          <t>2,79; 4,57</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,4</t>
+          <t>0,38; 2,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,63</t>
+          <t>2,9; 5,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,14</t>
+          <t>1,83; 3,47</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,29</t>
+          <t>0,73; 3,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,84</t>
+          <t>3,11; 6,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,27</t>
+          <t>2,36; 4,54</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,49</t>
+          <t>0,83; 1,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,74</t>
+          <t>3,65; 4,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,16; 2,98</t>
+          <t>2,32; 3,07</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12766</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12766</t>
+          <t>16059</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5077; 29381</t>
+          <t>6648; 31506</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4930; 26330</t>
+          <t>6839; 34341</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12147</t>
+          <t>14328</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1074; 13483</t>
+          <t>1378; 14461</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3115; 15809</t>
+          <t>4249; 18088</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6261; 21200</t>
+          <t>7377; 23918</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24476</t>
+          <t>25865</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2757; 15391</t>
+          <t>2801; 15543</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11744; 24564</t>
+          <t>12484; 26507</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16953; 34250</t>
+          <t>17527; 35638</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>41671</t>
+          <t>41031</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48905</t>
+          <t>48423</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1962; 15200</t>
+          <t>3127; 15523</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31046; 60373</t>
+          <t>32247; 51354</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27368; 67966</t>
+          <t>37497; 61838</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29562</t>
+          <t>32439</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39745</t>
+          <t>43455</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5386; 17887</t>
+          <t>5771; 18924</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21886; 37952</t>
+          <t>24084; 42425</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30863; 51496</t>
+          <t>33750; 55259</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>21714</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1589; 8778</t>
+          <t>1526; 8765</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6464; 28114</t>
+          <t>12698; 25648</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10048; 30578</t>
+          <t>15423; 29240</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17878</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>25145</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2158; 9238</t>
+          <t>2264; 10033</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12835; 24742</t>
+          <t>14401; 28148</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16382; 30074</t>
+          <t>18217; 35022</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>143493</t>
+          <t>155081</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>180887</t>
+          <t>194989</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>25203; 51393</t>
+          <t>29269; 55553</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>116137; 172756</t>
+          <t>135676; 179204</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>153163; 211769</t>
+          <t>168200; 222488</t>
         </is>
       </c>
     </row>
